--- a/tpl/flyfish_template.xlsx
+++ b/tpl/flyfish_template.xlsx
@@ -779,7 +779,7 @@
       <formula1>='Справочники'!$G$2:$G$4</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Нет в списке" error="Значения нет в списке — можно оставить своё" prompt="Список — подсказка: можно вписать производителя, которого в нём нет" type="list" errorStyle="warning">
-      <formula1>='Справочники'!$I$2:$I$22</formula1>
+      <formula1>='Справочники'!$I$2:$I$21</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -914,7 +914,7 @@
       <formula1>='Справочники'!$G$2:$G$4</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Нет в списке" error="Значения нет в списке — можно оставить своё" prompt="Список — подсказка: можно вписать производителя, которого в нём нет" type="list" errorStyle="warning">
-      <formula1>='Справочники'!$I$2:$I$22</formula1>
+      <formula1>='Справочники'!$I$2:$I$21</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1043,7 +1043,7 @@
       <formula1>='Справочники'!$H$2:$H$3</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Нет в списке" error="Значения нет в списке — можно оставить своё" prompt="Список — подсказка: можно вписать производителя, которого в нём нет" type="list" errorStyle="warning">
-      <formula1>='Справочники'!$I$2:$I$22</formula1>
+      <formula1>='Справочники'!$I$2:$I$21</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1444,13 +1444,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>GAFF</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
